--- a/tame_output/ON/bt/strategyON_20231216.xlsx
+++ b/tame_output/ON/bt/strategyON_20231216.xlsx
@@ -992,7 +992,7 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-6.0%</t>
+          <t>-6.1%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -1012,7 +1012,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>494.4%</t>
+          <t>494.3%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
@@ -1042,7 +1042,7 @@
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>-94.5%</t>
+          <t>-94.7%</t>
         </is>
       </c>
     </row>
@@ -1195,7 +1195,7 @@
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>-10.5%</t>
+          <t>-10.6%</t>
         </is>
       </c>
     </row>
@@ -1217,7 +1217,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>0.62</t>
+          <t>0.61</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1348,7 +1348,7 @@
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>-27.6%</t>
+          <t>-27.7%</t>
         </is>
       </c>
     </row>
@@ -1360,7 +1360,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>115.8%</t>
+          <t>115.7%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1451,7 +1451,7 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>111.5%</t>
+          <t>111.4%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>10.8%</t>
+          <t>10.7%</t>
         </is>
       </c>
     </row>
@@ -42473,7 +42473,7 @@
         <v>45243</v>
       </c>
       <c r="B1781" t="n">
-        <v>3.120443325780868</v>
+        <v>3.120443325780867</v>
       </c>
       <c r="C1781" t="n">
         <v>3.067121317473999</v>
@@ -42772,7 +42772,7 @@
         <v>45256</v>
       </c>
       <c r="B1794" t="n">
-        <v>3.147014107714844</v>
+        <v>3.147014107714843</v>
       </c>
       <c r="C1794" t="n">
         <v>3.076099785321473</v>
@@ -42887,7 +42887,7 @@
         <v>45261</v>
       </c>
       <c r="B1799" t="n">
-        <v>3.18551435596348</v>
+        <v>3.185514355963481</v>
       </c>
       <c r="C1799" t="n">
         <v>3.080810681773143</v>
@@ -42910,7 +42910,7 @@
         <v>45262</v>
       </c>
       <c r="B1800" t="n">
-        <v>3.199276732583695</v>
+        <v>3.199276732583696</v>
       </c>
       <c r="C1800" t="n">
         <v>3.083027154880305</v>
@@ -42933,7 +42933,7 @@
         <v>45263</v>
       </c>
       <c r="B1801" t="n">
-        <v>3.238767863742725</v>
+        <v>3.238767863742726</v>
       </c>
       <c r="C1801" t="n">
         <v>3.090561751225397</v>
@@ -42956,7 +42956,7 @@
         <v>45264</v>
       </c>
       <c r="B1802" t="n">
-        <v>3.260068416589525</v>
+        <v>3.260068416589526</v>
       </c>
       <c r="C1802" t="n">
         <v>3.091984762198855</v>
@@ -42979,7 +42979,7 @@
         <v>45265</v>
       </c>
       <c r="B1803" t="n">
-        <v>3.306739876872958</v>
+        <v>3.306739876872959</v>
       </c>
       <c r="C1803" t="n">
         <v>3.093661836664541</v>
@@ -43002,7 +43002,7 @@
         <v>45266</v>
       </c>
       <c r="B1804" t="n">
-        <v>3.31216459594633</v>
+        <v>3.312164595946331</v>
       </c>
       <c r="C1804" t="n">
         <v>3.089601258113999</v>
@@ -43025,7 +43025,7 @@
         <v>45267</v>
       </c>
       <c r="B1805" t="n">
-        <v>3.300520058336486</v>
+        <v>3.300520058336487</v>
       </c>
       <c r="C1805" t="n">
         <v>3.094821397458016</v>
@@ -43071,7 +43071,7 @@
         <v>45269</v>
       </c>
       <c r="B1807" t="n">
-        <v>3.311781349308504</v>
+        <v>3.311781349308505</v>
       </c>
       <c r="C1807" t="n">
         <v>3.093376148078457</v>
@@ -43094,7 +43094,7 @@
         <v>45270</v>
       </c>
       <c r="B1808" t="n">
-        <v>3.271427670257517</v>
+        <v>3.271427670257518</v>
       </c>
       <c r="C1808" t="n">
         <v>3.090839823094569</v>
@@ -43117,7 +43117,7 @@
         <v>45271</v>
       </c>
       <c r="B1809" t="n">
-        <v>3.252962387441541</v>
+        <v>3.252962387441542</v>
       </c>
       <c r="C1809" t="n">
         <v>3.109254206721308</v>
@@ -43140,7 +43140,7 @@
         <v>45272</v>
       </c>
       <c r="B1810" t="n">
-        <v>3.241257540662169</v>
+        <v>3.24125754066217</v>
       </c>
       <c r="C1810" t="n">
         <v>3.119070330776787</v>
@@ -43163,7 +43163,7 @@
         <v>45273</v>
       </c>
       <c r="B1811" t="n">
-        <v>3.285495323543325</v>
+        <v>3.285495323543326</v>
       </c>
       <c r="C1811" t="n">
         <v>3.132597942828719</v>
@@ -43186,7 +43186,7 @@
         <v>45274</v>
       </c>
       <c r="B1812" t="n">
-        <v>3.287726162978609</v>
+        <v>3.28772616297861</v>
       </c>
       <c r="C1812" t="n">
         <v>3.139185323079984</v>
@@ -43209,22 +43209,22 @@
         <v>45275</v>
       </c>
       <c r="B1813" t="n">
-        <v>3.096959801707693</v>
+        <v>3.096959801707694</v>
       </c>
       <c r="C1813" t="n">
         <v>3.128096071514691</v>
       </c>
       <c r="D1813" t="n">
-        <v>0.4787908807392797</v>
+        <v>0.4775389522277423</v>
       </c>
       <c r="E1813" t="n">
-        <v>3.319255999496656</v>
+        <v>3.318755228092041</v>
       </c>
       <c r="F1813" t="n">
-        <v>1.817101040693115</v>
+        <v>1.815849112181578</v>
       </c>
       <c r="G1813" t="n">
-        <v>4.218356695930561</v>
+        <v>4.217605538823639</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20231216.xlsx
+++ b/tame_output/ON/bt/strategyON_20231216.xlsx
@@ -42473,7 +42473,7 @@
         <v>45243</v>
       </c>
       <c r="B1781" t="n">
-        <v>3.120443325780867</v>
+        <v>3.120443325780868</v>
       </c>
       <c r="C1781" t="n">
         <v>3.067121317473999</v>
@@ -42772,7 +42772,7 @@
         <v>45256</v>
       </c>
       <c r="B1794" t="n">
-        <v>3.147014107714843</v>
+        <v>3.147014107714844</v>
       </c>
       <c r="C1794" t="n">
         <v>3.076099785321473</v>
@@ -42887,7 +42887,7 @@
         <v>45261</v>
       </c>
       <c r="B1799" t="n">
-        <v>3.185514355963481</v>
+        <v>3.18551435596348</v>
       </c>
       <c r="C1799" t="n">
         <v>3.080810681773143</v>
@@ -42910,7 +42910,7 @@
         <v>45262</v>
       </c>
       <c r="B1800" t="n">
-        <v>3.199276732583696</v>
+        <v>3.199276732583695</v>
       </c>
       <c r="C1800" t="n">
         <v>3.083027154880305</v>
@@ -42933,7 +42933,7 @@
         <v>45263</v>
       </c>
       <c r="B1801" t="n">
-        <v>3.238767863742726</v>
+        <v>3.238767863742725</v>
       </c>
       <c r="C1801" t="n">
         <v>3.090561751225397</v>
@@ -42956,7 +42956,7 @@
         <v>45264</v>
       </c>
       <c r="B1802" t="n">
-        <v>3.260068416589526</v>
+        <v>3.260068416589525</v>
       </c>
       <c r="C1802" t="n">
         <v>3.091984762198855</v>
@@ -42979,7 +42979,7 @@
         <v>45265</v>
       </c>
       <c r="B1803" t="n">
-        <v>3.306739876872959</v>
+        <v>3.306739876872958</v>
       </c>
       <c r="C1803" t="n">
         <v>3.093661836664541</v>
@@ -43002,7 +43002,7 @@
         <v>45266</v>
       </c>
       <c r="B1804" t="n">
-        <v>3.312164595946331</v>
+        <v>3.31216459594633</v>
       </c>
       <c r="C1804" t="n">
         <v>3.089601258113999</v>
@@ -43025,7 +43025,7 @@
         <v>45267</v>
       </c>
       <c r="B1805" t="n">
-        <v>3.300520058336487</v>
+        <v>3.300520058336486</v>
       </c>
       <c r="C1805" t="n">
         <v>3.094821397458016</v>
@@ -43071,7 +43071,7 @@
         <v>45269</v>
       </c>
       <c r="B1807" t="n">
-        <v>3.311781349308505</v>
+        <v>3.311781349308504</v>
       </c>
       <c r="C1807" t="n">
         <v>3.093376148078457</v>
@@ -43094,7 +43094,7 @@
         <v>45270</v>
       </c>
       <c r="B1808" t="n">
-        <v>3.271427670257518</v>
+        <v>3.271427670257517</v>
       </c>
       <c r="C1808" t="n">
         <v>3.090839823094569</v>
@@ -43117,7 +43117,7 @@
         <v>45271</v>
       </c>
       <c r="B1809" t="n">
-        <v>3.252962387441542</v>
+        <v>3.252962387441541</v>
       </c>
       <c r="C1809" t="n">
         <v>3.109254206721308</v>
@@ -43140,7 +43140,7 @@
         <v>45272</v>
       </c>
       <c r="B1810" t="n">
-        <v>3.24125754066217</v>
+        <v>3.241257540662169</v>
       </c>
       <c r="C1810" t="n">
         <v>3.119070330776787</v>
@@ -43163,7 +43163,7 @@
         <v>45273</v>
       </c>
       <c r="B1811" t="n">
-        <v>3.285495323543326</v>
+        <v>3.285495323543325</v>
       </c>
       <c r="C1811" t="n">
         <v>3.132597942828719</v>
@@ -43186,7 +43186,7 @@
         <v>45274</v>
       </c>
       <c r="B1812" t="n">
-        <v>3.28772616297861</v>
+        <v>3.287726162978609</v>
       </c>
       <c r="C1812" t="n">
         <v>3.139185323079984</v>
@@ -43209,22 +43209,22 @@
         <v>45275</v>
       </c>
       <c r="B1813" t="n">
-        <v>3.096959801707694</v>
+        <v>3.096959801707693</v>
       </c>
       <c r="C1813" t="n">
         <v>3.128096071514691</v>
       </c>
       <c r="D1813" t="n">
-        <v>0.4775389522277423</v>
+        <v>0.4773802201691228</v>
       </c>
       <c r="E1813" t="n">
-        <v>3.318755228092041</v>
+        <v>3.318691735268593</v>
       </c>
       <c r="F1813" t="n">
-        <v>1.815849112181578</v>
+        <v>1.815690380122958</v>
       </c>
       <c r="G1813" t="n">
-        <v>4.217605538823639</v>
+        <v>4.217510299588468</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20231216.xlsx
+++ b/tame_output/ON/bt/strategyON_20231216.xlsx
@@ -901,17 +901,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-19.9%</t>
+          <t>-21.6%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>74.7%</t>
+          <t>74.6%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.27</t>
+          <t>-0.29</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -939,7 +939,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>66.2%</t>
+          <t>66.0%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -977,7 +977,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>16.5%</t>
+          <t>16.2%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -992,7 +992,7 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-6.1%</t>
+          <t>-8.5%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -1012,7 +1012,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>494.3%</t>
+          <t>489.7%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
@@ -1042,7 +1042,7 @@
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>-94.7%</t>
+          <t>-105.2%</t>
         </is>
       </c>
     </row>
@@ -1054,22 +1054,22 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>78.9%</t>
+          <t>77.4%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>41.2%</t>
+          <t>41.1%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>1.92</t>
+          <t>1.88</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>58.2%</t>
+          <t>58.1%</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -1087,7 +1087,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>45.6%</t>
+          <t>45.5%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1130,7 +1130,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>11.1%</t>
+          <t>11.0%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1145,7 +1145,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>75.5%</t>
+          <t>73.6%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1155,7 +1155,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>2.2</t>
+          <t>2.1</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-17.9%</t>
+          <t>-17.8%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
@@ -1195,7 +1195,7 @@
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>-10.6%</t>
+          <t>-14.8%</t>
         </is>
       </c>
     </row>
@@ -1207,17 +1207,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>28.5%</t>
+          <t>25.9%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>46.3%</t>
+          <t>46.1%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>0.61</t>
+          <t>0.56</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1245,7 +1245,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>56.7%</t>
+          <t>56.2%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1283,7 +1283,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>8.4%</t>
+          <t>8.2%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1293,22 +1293,22 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>-0.2</t>
+          <t>-0.1</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>42.1%</t>
+          <t>38.4%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>37.8%</t>
+          <t>37.7%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>1.1</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -1318,7 +1318,7 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>17.7%</t>
+          <t>18.5%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
@@ -1348,7 +1348,7 @@
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>-27.7%</t>
+          <t>-38.3%</t>
         </is>
       </c>
     </row>
@@ -1360,7 +1360,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>115.7%</t>
+          <t>113.0%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1370,12 +1370,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2.92</t>
+          <t>2.85</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>59.8%</t>
+          <t>59.7%</t>
         </is>
       </c>
       <c r="F7" t="n">
@@ -1398,7 +1398,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>37.6%</t>
+          <t>37.5%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1436,7 +1436,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>10.7%</t>
+          <t>10.6%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1451,7 +1451,7 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>111.4%</t>
+          <t>108.1%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1461,7 +1461,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>3.4</t>
+          <t>3.3</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1471,7 +1471,7 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-13.9%</t>
+          <t>-13.7%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>10.7%</t>
+          <t>4.4%</t>
         </is>
       </c>
     </row>
@@ -43215,16 +43215,16 @@
         <v>3.128096071514691</v>
       </c>
       <c r="D1813" t="n">
-        <v>0.4773802201691228</v>
+        <v>0.3717532266054241</v>
       </c>
       <c r="E1813" t="n">
-        <v>3.318691735268593</v>
+        <v>3.276440937843114</v>
       </c>
       <c r="F1813" t="n">
-        <v>1.815690380122958</v>
+        <v>1.710063386559259</v>
       </c>
       <c r="G1813" t="n">
-        <v>4.217510299588468</v>
+        <v>4.154134103450248</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20231216.xlsx
+++ b/tame_output/ON/bt/strategyON_20231216.xlsx
@@ -595,17 +595,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>48.2%</t>
+          <t>48.9%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>67.3%</t>
+          <t>67.2%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.72</t>
+          <t>0.73</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -628,7 +628,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>67.0%</t>
+          <t>66.8%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -676,7 +676,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-11.7%</t>
+          <t>-11.6%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -736,7 +736,7 @@
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>86.1%</t>
+          <t>88.0%</t>
         </is>
       </c>
     </row>
@@ -839,7 +839,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>67.2%</t>
+          <t>67.1%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -901,12 +901,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-21.6%</t>
+          <t>-21.7%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>74.6%</t>
+          <t>74.8%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -934,17 +934,17 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>83.0%</t>
+          <t>83.3%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>66.0%</t>
+          <t>66.2%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>99.5%</t>
+          <t>99.6%</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -977,12 +977,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>16.2%</t>
+          <t>17.0%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-22.8%</t>
+          <t>-22.2%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-8.5%</t>
+          <t>-8.0%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>61.1%</t>
+          <t>61.2%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1012,12 +1012,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>489.7%</t>
+          <t>485.4%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-163.9%</t>
+          <t>-163.2%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1042,7 +1042,7 @@
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>-105.2%</t>
+          <t>-105.0%</t>
         </is>
       </c>
     </row>
@@ -1059,7 +1059,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>41.1%</t>
+          <t>41.2%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1087,7 +1087,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>45.5%</t>
+          <t>45.6%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1097,7 +1097,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>84.1%</t>
+          <t>84.5%</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -1107,11 +1107,11 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>2023-10-31</t>
+          <t>2023-11-01</t>
         </is>
       </c>
       <c r="N5" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
@@ -1145,7 +1145,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>73.6%</t>
+          <t>74.0%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1155,7 +1155,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>2.1</t>
+          <t>2.2</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-17.8%</t>
+          <t>-18.0%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
@@ -1195,7 +1195,7 @@
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>-14.8%</t>
+          <t>-14.7%</t>
         </is>
       </c>
     </row>
@@ -1207,17 +1207,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>25.9%</t>
+          <t>28.3%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>46.1%</t>
+          <t>46.3%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>0.56</t>
+          <t>0.61</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1245,7 +1245,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>56.2%</t>
+          <t>56.6%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1283,7 +1283,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>8.2%</t>
+          <t>8.4%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1293,12 +1293,12 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>-0.1</t>
+          <t>-0.2</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>38.4%</t>
+          <t>41.9%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1308,7 +1308,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>1.1</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -1318,7 +1318,7 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>18.5%</t>
+          <t>17.7%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
@@ -1348,7 +1348,7 @@
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>-38.3%</t>
+          <t>-28.3%</t>
         </is>
       </c>
     </row>
@@ -1360,7 +1360,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>113.0%</t>
+          <t>115.6%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1370,12 +1370,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2.85</t>
+          <t>2.92</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>59.7%</t>
+          <t>59.8%</t>
         </is>
       </c>
       <c r="F7" t="n">
@@ -1398,7 +1398,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>37.5%</t>
+          <t>37.6%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1436,7 +1436,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>10.6%</t>
+          <t>10.7%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1451,7 +1451,7 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>108.1%</t>
+          <t>111.2%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1461,7 +1461,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>3.3</t>
+          <t>3.4</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1471,7 +1471,7 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-13.7%</t>
+          <t>-13.9%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>4.4%</t>
+          <t>10.3%</t>
         </is>
       </c>
     </row>
@@ -42203,10 +42203,10 @@
         <v>3.049962823512704</v>
       </c>
       <c r="D1769" t="n">
-        <v>-2.766702260747862</v>
+        <v>-2.86375498825365</v>
       </c>
       <c r="E1769" t="n">
-        <v>1.942925494899812</v>
+        <v>1.904104403897497</v>
       </c>
       <c r="F1769" t="n">
         <v>0.4428584067673121</v>
@@ -42226,10 +42226,10 @@
         <v>3.048277258176837</v>
       </c>
       <c r="D1770" t="n">
-        <v>-2.756710179821452</v>
+        <v>-2.853762907327241</v>
       </c>
       <c r="E1770" t="n">
-        <v>1.945236761934509</v>
+        <v>1.906415670932194</v>
       </c>
       <c r="F1770" t="n">
         <v>0.4528504876937213</v>
@@ -42249,10 +42249,10 @@
         <v>3.051179068073428</v>
       </c>
       <c r="D1771" t="n">
-        <v>-2.75726593487749</v>
+        <v>-2.854318662383279</v>
       </c>
       <c r="E1771" t="n">
-        <v>1.947916269808685</v>
+        <v>1.90909517880637</v>
       </c>
       <c r="F1771" t="n">
         <v>0.4512430739326433</v>
@@ -42272,10 +42272,10 @@
         <v>3.056704057212575</v>
       </c>
       <c r="D1772" t="n">
-        <v>-2.760480287290802</v>
+        <v>-2.85753301479659</v>
       </c>
       <c r="E1772" t="n">
-        <v>1.952155517982507</v>
+        <v>1.913334426980192</v>
       </c>
       <c r="F1772" t="n">
         <v>0.4512430739326433</v>
@@ -42295,10 +42295,10 @@
         <v>3.057781629850306</v>
       </c>
       <c r="D1773" t="n">
-        <v>-2.777488532693411</v>
+        <v>-2.874541260199199</v>
       </c>
       <c r="E1773" t="n">
-        <v>1.946429792459195</v>
+        <v>1.90760870145688</v>
       </c>
       <c r="F1773" t="n">
         <v>0.4542422089456171</v>
@@ -42318,10 +42318,10 @@
         <v>3.058531492021579</v>
       </c>
       <c r="D1774" t="n">
-        <v>-2.758528810242057</v>
+        <v>-2.855581537747845</v>
       </c>
       <c r="E1774" t="n">
-        <v>1.95476354361101</v>
+        <v>1.915942452608694</v>
       </c>
       <c r="F1774" t="n">
         <v>0.4542422089456171</v>
@@ -42341,10 +42341,10 @@
         <v>3.05676708948516</v>
       </c>
       <c r="D1775" t="n">
-        <v>-2.757294085639248</v>
+        <v>-2.854346813145036</v>
       </c>
       <c r="E1775" t="n">
-        <v>1.953493030915714</v>
+        <v>1.914671939913399</v>
       </c>
       <c r="F1775" t="n">
         <v>0.4542422089456171</v>
@@ -42364,10 +42364,10 @@
         <v>3.060334699322022</v>
       </c>
       <c r="D1776" t="n">
-        <v>-2.767328349462897</v>
+        <v>-2.864381076968685</v>
       </c>
       <c r="E1776" t="n">
-        <v>1.953046935223117</v>
+        <v>1.914225844220801</v>
       </c>
       <c r="F1776" t="n">
         <v>0.4542422089456171</v>
@@ -42387,10 +42387,10 @@
         <v>3.084316661211631</v>
       </c>
       <c r="D1777" t="n">
-        <v>-2.772367347760764</v>
+        <v>-2.869420075266552</v>
       </c>
       <c r="E1777" t="n">
-        <v>1.975013297793579</v>
+        <v>1.936192206791264</v>
       </c>
       <c r="F1777" t="n">
         <v>0.4492032106477504</v>
@@ -42410,10 +42410,10 @@
         <v>3.081785372698861</v>
       </c>
       <c r="D1778" t="n">
-        <v>-2.762547629600213</v>
+        <v>-2.859600357106001</v>
       </c>
       <c r="E1778" t="n">
-        <v>1.976409896545029</v>
+        <v>1.937588805542714</v>
       </c>
       <c r="F1778" t="n">
         <v>0.4556331508644378</v>
@@ -42433,10 +42433,10 @@
         <v>3.067033934702486</v>
       </c>
       <c r="D1779" t="n">
-        <v>-2.760746002761259</v>
+        <v>-2.857798730267047</v>
       </c>
       <c r="E1779" t="n">
-        <v>1.962379109284236</v>
+        <v>1.923558018281921</v>
       </c>
       <c r="F1779" t="n">
         <v>0.4556331508644378</v>
@@ -42456,10 +42456,10 @@
         <v>3.065147691018159</v>
       </c>
       <c r="D1780" t="n">
-        <v>-2.759757321017091</v>
+        <v>-2.856810048522879</v>
       </c>
       <c r="E1780" t="n">
-        <v>1.960888338297575</v>
+        <v>1.92206724729526</v>
       </c>
       <c r="F1780" t="n">
         <v>0.4556331508644378</v>
@@ -42479,10 +42479,10 @@
         <v>3.067121317473999</v>
       </c>
       <c r="D1781" t="n">
-        <v>-2.751760966495552</v>
+        <v>-2.848813694001341</v>
       </c>
       <c r="E1781" t="n">
-        <v>1.966060506562031</v>
+        <v>1.927239415559716</v>
       </c>
       <c r="F1781" t="n">
         <v>0.4636295053859764</v>
@@ -42502,10 +42502,10 @@
         <v>3.078959898064911</v>
       </c>
       <c r="D1782" t="n">
-        <v>-2.746777215823644</v>
+        <v>-2.843829943329432</v>
       </c>
       <c r="E1782" t="n">
-        <v>1.979892587421706</v>
+        <v>1.941071496419391</v>
       </c>
       <c r="F1782" t="n">
         <v>0.4686132560578851</v>
@@ -42525,10 +42525,10 @@
         <v>3.0856881010767</v>
       </c>
       <c r="D1783" t="n">
-        <v>-2.740391076874088</v>
+        <v>-2.837443804379876</v>
       </c>
       <c r="E1783" t="n">
-        <v>1.989175246013318</v>
+        <v>1.950354155011003</v>
       </c>
       <c r="F1783" t="n">
         <v>0.4686132560578851</v>
@@ -42548,10 +42548,10 @@
         <v>3.089704189836242</v>
       </c>
       <c r="D1784" t="n">
-        <v>-2.752196427192721</v>
+        <v>-2.849249154698509</v>
       </c>
       <c r="E1784" t="n">
-        <v>1.988469194645407</v>
+        <v>1.949648103643092</v>
       </c>
       <c r="F1784" t="n">
         <v>0.4568079057392525</v>
@@ -42571,10 +42571,10 @@
         <v>3.095651647446132</v>
       </c>
       <c r="D1785" t="n">
-        <v>-2.743464616414054</v>
+        <v>-2.840517343919843</v>
       </c>
       <c r="E1785" t="n">
-        <v>1.997909376566763</v>
+        <v>1.959088285564448</v>
       </c>
       <c r="F1785" t="n">
         <v>0.4655397165179187</v>
@@ -42594,10 +42594,10 @@
         <v>3.090962466394117</v>
       </c>
       <c r="D1786" t="n">
-        <v>-2.737127729769602</v>
+        <v>-2.834180457275391</v>
       </c>
       <c r="E1786" t="n">
-        <v>1.995754950172529</v>
+        <v>1.956933859170214</v>
       </c>
       <c r="F1786" t="n">
         <v>0.4655397165179187</v>
@@ -42617,10 +42617,10 @@
         <v>3.100925124196311</v>
       </c>
       <c r="D1787" t="n">
-        <v>-2.734593282042234</v>
+        <v>-2.831646009548022</v>
       </c>
       <c r="E1787" t="n">
-        <v>2.00673138706567</v>
+        <v>1.967910296063355</v>
       </c>
       <c r="F1787" t="n">
         <v>0.4655397165179187</v>
@@ -42640,10 +42640,10 @@
         <v>3.09333980438922</v>
       </c>
       <c r="D1788" t="n">
-        <v>-2.734669181022838</v>
+        <v>-2.831721908528627</v>
       </c>
       <c r="E1788" t="n">
-        <v>1.999115707666338</v>
+        <v>1.960294616664023</v>
       </c>
       <c r="F1788" t="n">
         <v>0.4663029772072456</v>
@@ -42663,10 +42663,10 @@
         <v>3.071104380179594</v>
       </c>
       <c r="D1789" t="n">
-        <v>-2.745171370582185</v>
+        <v>-2.842224098087974</v>
       </c>
       <c r="E1789" t="n">
-        <v>1.972679407632973</v>
+        <v>1.933858316630657</v>
       </c>
       <c r="F1789" t="n">
         <v>0.4558007876478989</v>
@@ -42686,10 +42686,10 @@
         <v>3.071805220025715</v>
       </c>
       <c r="D1790" t="n">
-        <v>-2.747004633261301</v>
+        <v>-2.84405736076709</v>
       </c>
       <c r="E1790" t="n">
-        <v>1.972646942407448</v>
+        <v>1.933825851405132</v>
       </c>
       <c r="F1790" t="n">
         <v>0.4558007876478989</v>
@@ -42709,10 +42709,10 @@
         <v>3.072322299854575</v>
       </c>
       <c r="D1791" t="n">
-        <v>-2.752013748322885</v>
+        <v>-2.849066475828674</v>
       </c>
       <c r="E1791" t="n">
-        <v>1.971160376211674</v>
+        <v>1.932339285209359</v>
       </c>
       <c r="F1791" t="n">
         <v>0.4548062100893642</v>
@@ -42732,10 +42732,10 @@
         <v>3.07155002509494</v>
       </c>
       <c r="D1792" t="n">
-        <v>-2.7557193049597</v>
+        <v>-2.852772032465488</v>
       </c>
       <c r="E1792" t="n">
-        <v>1.968905878797313</v>
+        <v>1.930084787794998</v>
       </c>
       <c r="F1792" t="n">
         <v>0.4529365348317293</v>
@@ -42755,10 +42755,10 @@
         <v>3.071969877157259</v>
       </c>
       <c r="D1793" t="n">
-        <v>-2.754486979602334</v>
+        <v>-2.851539707108123</v>
       </c>
       <c r="E1793" t="n">
-        <v>1.969818661002579</v>
+        <v>1.930997570000264</v>
       </c>
       <c r="F1793" t="n">
         <v>0.4535669112037669</v>
@@ -42778,10 +42778,10 @@
         <v>3.076099785321473</v>
       </c>
       <c r="D1794" t="n">
-        <v>-2.744158982586482</v>
+        <v>-2.841211710092271</v>
       </c>
       <c r="E1794" t="n">
-        <v>1.978079767973133</v>
+        <v>1.939258676970818</v>
       </c>
       <c r="F1794" t="n">
         <v>0.463894908219619</v>
@@ -42801,10 +42801,10 @@
         <v>3.082620445523309</v>
       </c>
       <c r="D1795" t="n">
-        <v>-2.744042647438926</v>
+        <v>-2.841095374944715</v>
       </c>
       <c r="E1795" t="n">
-        <v>1.984646962233992</v>
+        <v>1.945825871231677</v>
       </c>
       <c r="F1795" t="n">
         <v>0.4640112433671748</v>
@@ -42824,10 +42824,10 @@
         <v>3.079594415968698</v>
       </c>
       <c r="D1796" t="n">
-        <v>-2.745888057015794</v>
+        <v>-2.842940784521582</v>
       </c>
       <c r="E1796" t="n">
-        <v>1.980882768848633</v>
+        <v>1.942061677846318</v>
       </c>
       <c r="F1796" t="n">
         <v>0.4640112433671748</v>
@@ -42847,10 +42847,10 @@
         <v>3.079532703829831</v>
       </c>
       <c r="D1797" t="n">
-        <v>-2.744389624490695</v>
+        <v>-2.841442351996483</v>
       </c>
       <c r="E1797" t="n">
-        <v>1.981420429719807</v>
+        <v>1.942599338717491</v>
       </c>
       <c r="F1797" t="n">
         <v>0.4655096758922737</v>
@@ -42870,10 +42870,10 @@
         <v>3.080810681773143</v>
       </c>
       <c r="D1798" t="n">
-        <v>-2.752453876683429</v>
+        <v>-2.849506604189217</v>
       </c>
       <c r="E1798" t="n">
-        <v>1.979472706786025</v>
+        <v>1.940651615783709</v>
       </c>
       <c r="F1798" t="n">
         <v>0.4574454236995398</v>
@@ -42893,10 +42893,10 @@
         <v>3.080810681773143</v>
       </c>
       <c r="D1799" t="n">
-        <v>-2.753783844144641</v>
+        <v>-2.850836571650429</v>
       </c>
       <c r="E1799" t="n">
-        <v>1.97894071980154</v>
+        <v>1.940119628799224</v>
       </c>
       <c r="F1799" t="n">
         <v>0.4574454236995398</v>
@@ -42916,10 +42916,10 @@
         <v>3.083027154880305</v>
       </c>
       <c r="D1800" t="n">
-        <v>-2.52591916141113</v>
+        <v>-2.622971888916918</v>
       </c>
       <c r="E1800" t="n">
-        <v>2.072303066002106</v>
+        <v>2.033481974999791</v>
       </c>
       <c r="F1800" t="n">
         <v>0.4574454236995398</v>
@@ -42939,10 +42939,10 @@
         <v>3.090561751225397</v>
       </c>
       <c r="D1801" t="n">
-        <v>-2.277817597543913</v>
+        <v>-2.374870325049701</v>
       </c>
       <c r="E1801" t="n">
-        <v>2.179078287894085</v>
+        <v>2.14025719689177</v>
       </c>
       <c r="F1801" t="n">
         <v>0.4574454236995398</v>
@@ -42962,10 +42962,10 @@
         <v>3.091984762198855</v>
       </c>
       <c r="D1802" t="n">
-        <v>-1.980979198150582</v>
+        <v>-2.078031925656371</v>
       </c>
       <c r="E1802" t="n">
-        <v>2.299236658624875</v>
+        <v>2.260415567622559</v>
       </c>
       <c r="F1802" t="n">
         <v>0.5722999121806676</v>
@@ -42985,10 +42985,10 @@
         <v>3.093661836664541</v>
       </c>
       <c r="D1803" t="n">
-        <v>-1.677339641325146</v>
+        <v>-1.774392368830935</v>
       </c>
       <c r="E1803" t="n">
-        <v>2.422369555820736</v>
+        <v>2.38354846481842</v>
       </c>
       <c r="F1803" t="n">
         <v>0.5722999121806676</v>
@@ -43008,10 +43008,10 @@
         <v>3.089601258113999</v>
       </c>
       <c r="D1804" t="n">
-        <v>-1.388319034884437</v>
+        <v>-1.485371762390226</v>
       </c>
       <c r="E1804" t="n">
-        <v>2.533917219846477</v>
+        <v>2.495096128844161</v>
       </c>
       <c r="F1804" t="n">
         <v>0.5722999121806676</v>
@@ -43031,10 +43031,10 @@
         <v>3.094821397458016</v>
       </c>
       <c r="D1805" t="n">
-        <v>-1.10359910762054</v>
+        <v>-1.200651835126329</v>
       </c>
       <c r="E1805" t="n">
-        <v>2.653025330096054</v>
+        <v>2.614204239093738</v>
       </c>
       <c r="F1805" t="n">
         <v>0.8570198394445647</v>
@@ -43054,10 +43054,10 @@
         <v>3.100133560631823</v>
       </c>
       <c r="D1806" t="n">
-        <v>-0.8198374381289997</v>
+        <v>-0.9168901656347888</v>
       </c>
       <c r="E1806" t="n">
-        <v>2.771842161066477</v>
+        <v>2.733021070064161</v>
       </c>
       <c r="F1806" t="n">
         <v>0.8570198394445647</v>
@@ -43077,10 +43077,10 @@
         <v>3.093376148078457</v>
       </c>
       <c r="D1807" t="n">
-        <v>-0.558189043736359</v>
+        <v>-0.6552417712421481</v>
       </c>
       <c r="E1807" t="n">
-        <v>2.869744106270166</v>
+        <v>2.830923015267851</v>
       </c>
       <c r="F1807" t="n">
         <v>1.118668233837205</v>
@@ -43100,10 +43100,10 @@
         <v>3.090839823094569</v>
       </c>
       <c r="D1808" t="n">
-        <v>-0.2440226055970266</v>
+        <v>-0.3410753331028157</v>
       </c>
       <c r="E1808" t="n">
-        <v>2.992874356542012</v>
+        <v>2.954053265539696</v>
       </c>
       <c r="F1808" t="n">
         <v>1.432834671976538</v>
@@ -43123,10 +43123,10 @@
         <v>3.109254206721308</v>
       </c>
       <c r="D1809" t="n">
-        <v>-0.1215109014912542</v>
+        <v>-0.2185636289970433</v>
       </c>
       <c r="E1809" t="n">
-        <v>3.06029342181106</v>
+        <v>3.021472330808745</v>
       </c>
       <c r="F1809" t="n">
         <v>1.55534637608231</v>
@@ -43146,10 +43146,10 @@
         <v>3.119070330776787</v>
       </c>
       <c r="D1810" t="n">
-        <v>0.03987763243547415</v>
+        <v>-0.05717509507031493</v>
       </c>
       <c r="E1810" t="n">
-        <v>3.13466495943723</v>
+        <v>3.095843868434915</v>
       </c>
       <c r="F1810" t="n">
         <v>1.716734910009039</v>
@@ -43169,10 +43169,10 @@
         <v>3.132597942828719</v>
       </c>
       <c r="D1811" t="n">
-        <v>0.2196238235839804</v>
+        <v>0.1225710960781913</v>
       </c>
       <c r="E1811" t="n">
-        <v>3.220091047948564</v>
+        <v>3.181269956946248</v>
       </c>
       <c r="F1811" t="n">
         <v>1.716734910009039</v>
@@ -43192,10 +43192,10 @@
         <v>3.139185323079984</v>
       </c>
       <c r="D1812" t="n">
-        <v>0.3784247500552033</v>
+        <v>0.2813720225494142</v>
       </c>
       <c r="E1812" t="n">
-        <v>3.290198798788319</v>
+        <v>3.251377707786003</v>
       </c>
       <c r="F1812" t="n">
         <v>1.716734910009039</v>
@@ -43209,22 +43209,22 @@
         <v>45275</v>
       </c>
       <c r="B1813" t="n">
-        <v>3.096959801707693</v>
+        <v>3.115220237360361</v>
       </c>
       <c r="C1813" t="n">
         <v>3.128096071514691</v>
       </c>
       <c r="D1813" t="n">
-        <v>0.3717532266054241</v>
+        <v>0.374160480854791</v>
       </c>
       <c r="E1813" t="n">
-        <v>3.276440937843114</v>
+        <v>3.277403839542861</v>
       </c>
       <c r="F1813" t="n">
-        <v>1.710063386559259</v>
+        <v>1.809523368314415</v>
       </c>
       <c r="G1813" t="n">
-        <v>4.154134103450248</v>
+        <v>4.213810092503341</v>
       </c>
     </row>
   </sheetData>
